--- a/Excel/StockQuotation (3).xlsx
+++ b/Excel/StockQuotation (3).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>01/02/23 15:07:28</v>
+        <v>03/02/23 12:58:16</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1206.65</v>
+        <v>1201.75</v>
       </c>
       <c r="B7" t="str">
-        <v>9.13 (0.7624%)</v>
+        <v>-3.47 (-0.2879%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1207.9</v>
+        <v>1205.23</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1200.04</v>
+        <v>1196.56</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>556374650</v>
+        <v>435614522</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>8235308167.53</v>
+        <v>8936784860.96</v>
       </c>
     </row>
     <row r="9">
@@ -517,43 +517,43 @@
         <v>198</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="E10">
-        <v>1.5384615384615385</v>
+        <v>0.25316455696202533</v>
       </c>
       <c r="F10">
-        <v>196</v>
+        <v>197.5</v>
       </c>
       <c r="G10">
+        <v>198.5</v>
+      </c>
+      <c r="H10">
+        <v>197</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>926679</v>
+      </c>
+      <c r="L10">
+        <v>183244.338</v>
+      </c>
+      <c r="M10">
+        <v>127900</v>
+      </c>
+      <c r="N10">
         <v>198</v>
       </c>
-      <c r="H10">
-        <v>196</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>2730306</v>
-      </c>
-      <c r="L10">
-        <v>536589.1725</v>
-      </c>
-      <c r="M10">
-        <v>340500</v>
-      </c>
-      <c r="N10">
-        <v>197.5</v>
-      </c>
       <c r="O10">
-        <v>198</v>
+        <v>198.5</v>
       </c>
       <c r="P10">
-        <v>129400</v>
+        <v>132800</v>
       </c>
     </row>
     <row r="11">
@@ -564,16 +564,16 @@
         <v>-</v>
       </c>
       <c r="C11">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="D11">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E11">
-        <v>2.5210084033613445</v>
+        <v>-1.639344262295082</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="G11">
         <v>12.2</v>
@@ -588,22 +588,22 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>29432058</v>
+        <v>18412971</v>
       </c>
       <c r="L11">
-        <v>352949.4453</v>
+        <v>220380.516</v>
       </c>
       <c r="M11">
-        <v>2441500</v>
+        <v>287400</v>
       </c>
       <c r="N11">
+        <v>12</v>
+      </c>
+      <c r="O11">
         <v>12.1</v>
       </c>
-      <c r="O11">
-        <v>12.2</v>
-      </c>
       <c r="P11">
-        <v>2083900</v>
+        <v>1609600</v>
       </c>
     </row>
     <row r="12">
@@ -614,46 +614,46 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>160</v>
+        <v>161.5</v>
       </c>
       <c r="D12">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0.9463722397476341</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>160</v>
+        <v>161.5</v>
       </c>
       <c r="G12">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H12">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I12">
-        <v>62000</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>9827</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>4994969</v>
+        <v>2211193</v>
       </c>
       <c r="L12">
-        <v>794805.816</v>
+        <v>356945.837</v>
       </c>
       <c r="M12">
-        <v>413800</v>
+        <v>328100</v>
       </c>
       <c r="N12">
-        <v>159.5</v>
+        <v>161</v>
       </c>
       <c r="O12">
-        <v>160</v>
+        <v>161.5</v>
       </c>
       <c r="P12">
-        <v>513800</v>
+        <v>159400</v>
       </c>
     </row>
     <row r="13">
@@ -667,43 +667,43 @@
         <v>21.6</v>
       </c>
       <c r="D13">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="E13">
-        <v>-0.9174311926605505</v>
+        <v>0.9345794392523364</v>
       </c>
       <c r="F13">
+        <v>21.5</v>
+      </c>
+      <c r="G13">
+        <v>21.7</v>
+      </c>
+      <c r="H13">
+        <v>21.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>6836436</v>
+      </c>
+      <c r="L13">
+        <v>147330.1925</v>
+      </c>
+      <c r="M13">
+        <v>853900</v>
+      </c>
+      <c r="N13">
+        <v>21.5</v>
+      </c>
+      <c r="O13">
         <v>21.6</v>
       </c>
-      <c r="G13">
-        <v>21.8</v>
-      </c>
-      <c r="H13">
-        <v>21.3</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>10671559</v>
-      </c>
-      <c r="L13">
-        <v>230301.2862</v>
-      </c>
-      <c r="M13">
-        <v>502900</v>
-      </c>
-      <c r="N13">
-        <v>21.6</v>
-      </c>
-      <c r="O13">
-        <v>21.7</v>
-      </c>
       <c r="P13">
-        <v>905400</v>
+        <v>289200</v>
       </c>
     </row>
     <row r="14">
@@ -714,16 +714,16 @@
         <v>-</v>
       </c>
       <c r="C14">
-        <v>9.95</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E14">
-        <v>1.015228426395939</v>
+        <v>-0.9900990099009901</v>
       </c>
       <c r="F14">
-        <v>9.95</v>
+        <v>10.1</v>
       </c>
       <c r="G14">
         <v>10.1</v>
@@ -738,13 +738,13 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>4605144</v>
+        <v>1716422</v>
       </c>
       <c r="L14">
-        <v>46056.239649999996</v>
+        <v>17156.9141</v>
       </c>
       <c r="M14">
-        <v>688800</v>
+        <v>679000</v>
       </c>
       <c r="N14">
         <v>9.95</v>
@@ -753,7 +753,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>587900</v>
+        <v>413600</v>
       </c>
     </row>
     <row r="15">
@@ -764,19 +764,19 @@
         <v>-</v>
       </c>
       <c r="C15">
+        <v>8.4</v>
+      </c>
+      <c r="D15">
+        <v>-0.05</v>
+      </c>
+      <c r="E15">
+        <v>-0.591715976331361</v>
+      </c>
+      <c r="F15">
+        <v>8.4</v>
+      </c>
+      <c r="G15">
         <v>8.45</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>8.45</v>
-      </c>
-      <c r="G15">
-        <v>8.5</v>
       </c>
       <c r="H15">
         <v>8.4</v>
@@ -788,22 +788,22 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>13071616</v>
+        <v>6616794</v>
       </c>
       <c r="L15">
-        <v>110504.34855</v>
+        <v>55847.0761</v>
       </c>
       <c r="M15">
-        <v>4049300</v>
+        <v>5078500</v>
       </c>
       <c r="N15">
+        <v>8.4</v>
+      </c>
+      <c r="O15">
         <v>8.45</v>
       </c>
-      <c r="O15">
-        <v>8.5</v>
-      </c>
       <c r="P15">
-        <v>2125500</v>
+        <v>1630800</v>
       </c>
     </row>
     <row r="16">
@@ -814,22 +814,22 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>-2.985074626865672</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="G16">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="H16">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -838,22 +838,22 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>55318924</v>
+        <v>65572992</v>
       </c>
       <c r="L16">
-        <v>220823.85012000002</v>
+        <v>257050.73036000002</v>
       </c>
       <c r="M16">
-        <v>2923600</v>
+        <v>1628200</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="O16">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="P16">
-        <v>4863900</v>
+        <v>2800600</v>
       </c>
     </row>
     <row r="17">
@@ -864,22 +864,22 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="D17">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>1.694915254237288</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="G17">
         <v>24</v>
       </c>
       <c r="H17">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -888,22 +888,22 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>16211355</v>
+        <v>9578760</v>
       </c>
       <c r="L17">
-        <v>386839.27310000005</v>
+        <v>228593.6587</v>
       </c>
       <c r="M17">
-        <v>2575100</v>
+        <v>1523800</v>
       </c>
       <c r="N17">
+        <v>23.8</v>
+      </c>
+      <c r="O17">
         <v>23.9</v>
       </c>
-      <c r="O17">
-        <v>24</v>
-      </c>
       <c r="P17">
-        <v>3649400</v>
+        <v>474400</v>
       </c>
     </row>
     <row r="18">
@@ -917,16 +917,16 @@
         <v>173.5</v>
       </c>
       <c r="D18">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="E18">
-        <v>-0.28735632183908044</v>
+        <v>-0.5730659025787965</v>
       </c>
       <c r="F18">
         <v>174</v>
       </c>
       <c r="G18">
-        <v>175.5</v>
+        <v>175</v>
       </c>
       <c r="H18">
         <v>173.5</v>
@@ -938,13 +938,13 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>365379</v>
+        <v>254316</v>
       </c>
       <c r="L18">
-        <v>63615.27</v>
+        <v>44194.1755</v>
       </c>
       <c r="M18">
-        <v>105600</v>
+        <v>52200</v>
       </c>
       <c r="N18">
         <v>173.5</v>
@@ -953,7 +953,7 @@
         <v>174</v>
       </c>
       <c r="P18">
-        <v>82800</v>
+        <v>58700</v>
       </c>
     </row>
     <row r="19">
@@ -964,19 +964,19 @@
         <v>-</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="D19">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="E19">
-        <v>0.40160642570281124</v>
+        <v>-0.4</v>
       </c>
       <c r="F19">
         <v>5</v>
       </c>
       <c r="G19">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>4.98</v>
@@ -988,22 +988,22 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>32124912</v>
+        <v>3485277</v>
       </c>
       <c r="L19">
-        <v>160765.0349</v>
+        <v>17380.11324</v>
       </c>
       <c r="M19">
-        <v>8247500</v>
+        <v>4818900</v>
       </c>
       <c r="N19">
+        <v>4.98</v>
+      </c>
+      <c r="O19">
         <v>5</v>
       </c>
-      <c r="O19">
-        <v>5.05</v>
-      </c>
       <c r="P19">
-        <v>14373300</v>
+        <v>3493200</v>
       </c>
     </row>
     <row r="20">
@@ -1014,46 +1014,46 @@
         <v>-</v>
       </c>
       <c r="C20">
-        <v>60.25</v>
+        <v>64</v>
       </c>
       <c r="D20">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="E20">
-        <v>-0.4132231404958678</v>
+        <v>-1.5384615384615385</v>
       </c>
       <c r="F20">
-        <v>60.25</v>
+        <v>64.5</v>
       </c>
       <c r="G20">
-        <v>61.25</v>
+        <v>65</v>
       </c>
       <c r="H20">
-        <v>59.75</v>
+        <v>63.75</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>154800</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>10017.94392</v>
       </c>
       <c r="K20">
-        <v>8461192</v>
+        <v>8214450</v>
       </c>
       <c r="L20">
-        <v>512476.504</v>
+        <v>528159.57017</v>
       </c>
       <c r="M20">
-        <v>346500</v>
+        <v>125100</v>
       </c>
       <c r="N20">
-        <v>60.25</v>
+        <v>64</v>
       </c>
       <c r="O20">
-        <v>60.5</v>
+        <v>64.25</v>
       </c>
       <c r="P20">
-        <v>346600</v>
+        <v>90600</v>
       </c>
     </row>
     <row r="21">
@@ -1067,19 +1067,19 @@
         <v>73.5</v>
       </c>
       <c r="D21">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="E21">
-        <v>1.0309278350515463</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="F21">
-        <v>72.5</v>
+        <v>72.75</v>
       </c>
       <c r="G21">
-        <v>73.75</v>
+        <v>74</v>
       </c>
       <c r="H21">
-        <v>72.5</v>
+        <v>72.75</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1088,13 +1088,13 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>1003190</v>
+        <v>802203</v>
       </c>
       <c r="L21">
-        <v>73494.0175</v>
+        <v>58812.5405</v>
       </c>
       <c r="M21">
-        <v>118700</v>
+        <v>85100</v>
       </c>
       <c r="N21">
         <v>73.25</v>
@@ -1103,7 +1103,7 @@
         <v>73.5</v>
       </c>
       <c r="P21">
-        <v>45800</v>
+        <v>37400</v>
       </c>
     </row>
     <row r="22">
@@ -1114,46 +1114,46 @@
         <v>-</v>
       </c>
       <c r="C22">
+        <v>68</v>
+      </c>
+      <c r="D22">
+        <v>-0.5</v>
+      </c>
+      <c r="E22">
+        <v>-0.7299270072992701</v>
+      </c>
+      <c r="F22">
         <v>68.75</v>
       </c>
-      <c r="D22">
-        <v>0.5</v>
-      </c>
-      <c r="E22">
-        <v>0.7326007326007326</v>
-      </c>
-      <c r="F22">
-        <v>68.5</v>
-      </c>
       <c r="G22">
-        <v>69</v>
+        <v>68.75</v>
       </c>
       <c r="H22">
+        <v>68</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>3221568</v>
+      </c>
+      <c r="L22">
+        <v>220126.521</v>
+      </c>
+      <c r="M22">
+        <v>1284000</v>
+      </c>
+      <c r="N22">
+        <v>68</v>
+      </c>
+      <c r="O22">
         <v>68.25</v>
       </c>
-      <c r="I22">
-        <v>100000</v>
-      </c>
-      <c r="J22">
-        <v>6825</v>
-      </c>
-      <c r="K22">
-        <v>3871502</v>
-      </c>
-      <c r="L22">
-        <v>265346.21025</v>
-      </c>
-      <c r="M22">
-        <v>240000</v>
-      </c>
-      <c r="N22">
-        <v>68.75</v>
-      </c>
-      <c r="O22">
-        <v>69</v>
-      </c>
       <c r="P22">
-        <v>533700</v>
+        <v>311600</v>
       </c>
     </row>
     <row r="23">
@@ -1164,16 +1164,16 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="D23">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E23">
-        <v>0.5714285714285714</v>
+        <v>-1.1299435028248588</v>
       </c>
       <c r="F23">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="G23">
         <v>17.7</v>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>25537371</v>
+        <v>8304490</v>
       </c>
       <c r="L23">
-        <v>449460.9193</v>
+        <v>146039.773</v>
       </c>
       <c r="M23">
-        <v>9120400</v>
+        <v>9742600</v>
       </c>
       <c r="N23">
         <v>17.5</v>
@@ -1203,7 +1203,7 @@
         <v>17.6</v>
       </c>
       <c r="P23">
-        <v>3548600</v>
+        <v>1840600</v>
       </c>
     </row>
     <row r="24">
@@ -1214,13 +1214,13 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>9.95</v>
+        <v>9.9</v>
       </c>
       <c r="D24">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>0.5050505050505051</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>9.9</v>
@@ -1229,7 +1229,7 @@
         <v>9.95</v>
       </c>
       <c r="H24">
-        <v>9.85</v>
+        <v>9.8</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>20863046</v>
+        <v>23912903</v>
       </c>
       <c r="L24">
-        <v>206502.06355000002</v>
+        <v>236162.3487</v>
       </c>
       <c r="M24">
-        <v>4075800</v>
+        <v>947900</v>
       </c>
       <c r="N24">
         <v>9.9</v>
@@ -1253,7 +1253,7 @@
         <v>9.95</v>
       </c>
       <c r="P24">
-        <v>3549300</v>
+        <v>6180400</v>
       </c>
     </row>
     <row r="25">
@@ -1264,46 +1264,46 @@
         <v>-</v>
       </c>
       <c r="C25">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F25">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G25">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H25">
+        <v>11.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>2285421</v>
+      </c>
+      <c r="L25">
+        <v>27429.3772</v>
+      </c>
+      <c r="M25">
+        <v>358100</v>
+      </c>
+      <c r="N25">
         <v>12</v>
       </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>4635867</v>
-      </c>
-      <c r="L25">
-        <v>56101.162899999996</v>
-      </c>
-      <c r="M25">
-        <v>358800</v>
-      </c>
-      <c r="N25">
+      <c r="O25">
         <v>12.1</v>
       </c>
-      <c r="O25">
-        <v>12.2</v>
-      </c>
       <c r="P25">
-        <v>2410200</v>
+        <v>1005200</v>
       </c>
     </row>
     <row r="26">
@@ -1317,19 +1317,19 @@
         <v>28.25</v>
       </c>
       <c r="D26">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="E26">
-        <v>0.8928571428571429</v>
+        <v>-0.8771929824561403</v>
       </c>
       <c r="F26">
-        <v>28</v>
+        <v>28.25</v>
       </c>
       <c r="G26">
         <v>28.5</v>
       </c>
       <c r="H26">
-        <v>28</v>
+        <v>28.25</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>1722724</v>
+        <v>1108746</v>
       </c>
       <c r="L26">
-        <v>48646.9095</v>
+        <v>31330.526</v>
       </c>
       <c r="M26">
-        <v>510900</v>
+        <v>639800</v>
       </c>
       <c r="N26">
         <v>28.25</v>
@@ -1353,7 +1353,7 @@
         <v>28.5</v>
       </c>
       <c r="P26">
-        <v>2873400</v>
+        <v>1398300</v>
       </c>
     </row>
     <row r="27">
@@ -1364,7 +1364,7 @@
         <v>-</v>
       </c>
       <c r="C27">
-        <v>33.25</v>
+        <v>33</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1373,37 +1373,37 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>33.25</v>
+        <v>33</v>
       </c>
       <c r="G27">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="H27">
+        <v>32.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>37092275</v>
+      </c>
+      <c r="L27">
+        <v>1217492.49675</v>
+      </c>
+      <c r="M27">
+        <v>13678200</v>
+      </c>
+      <c r="N27">
+        <v>32.75</v>
+      </c>
+      <c r="O27">
         <v>33</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>21001307</v>
-      </c>
-      <c r="L27">
-        <v>697562.74825</v>
-      </c>
-      <c r="M27">
-        <v>16988000</v>
-      </c>
-      <c r="N27">
-        <v>33</v>
-      </c>
-      <c r="O27">
-        <v>33.25</v>
-      </c>
       <c r="P27">
-        <v>9901700</v>
+        <v>10779800</v>
       </c>
     </row>
     <row r="28">
@@ -1414,22 +1414,22 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D28">
-        <v>1.5</v>
+        <v>-4</v>
       </c>
       <c r="E28">
-        <v>0.8746355685131195</v>
+        <v>-2.3529411764705883</v>
       </c>
       <c r="F28">
-        <v>172</v>
+        <v>169.5</v>
       </c>
       <c r="G28">
-        <v>173.5</v>
+        <v>169.5</v>
       </c>
       <c r="H28">
-        <v>172</v>
+        <v>164.5</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1438,22 +1438,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>3978258</v>
+        <v>20392736</v>
       </c>
       <c r="L28">
-        <v>687599.3705</v>
+        <v>3387949.05</v>
       </c>
       <c r="M28">
-        <v>548400</v>
+        <v>773000</v>
       </c>
       <c r="N28">
-        <v>172.5</v>
+        <v>166</v>
       </c>
       <c r="O28">
-        <v>173</v>
+        <v>166.5</v>
       </c>
       <c r="P28">
-        <v>400400</v>
+        <v>252600</v>
       </c>
     </row>
     <row r="29">
@@ -1464,7 +1464,7 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G29">
         <v>2.38</v>
@@ -1488,22 +1488,22 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>9490948</v>
+        <v>18778190</v>
       </c>
       <c r="L29">
-        <v>22351.44492</v>
+        <v>44348.56588</v>
       </c>
       <c r="M29">
-        <v>6786000</v>
+        <v>1974200</v>
       </c>
       <c r="N29">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O29">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="P29">
-        <v>2626000</v>
+        <v>13838000</v>
       </c>
     </row>
     <row r="30">
@@ -1514,46 +1514,46 @@
         <v>-</v>
       </c>
       <c r="C30">
+        <v>43.25</v>
+      </c>
+      <c r="D30">
+        <v>0.25</v>
+      </c>
+      <c r="E30">
+        <v>0.5813953488372093</v>
+      </c>
+      <c r="F30">
+        <v>42.75</v>
+      </c>
+      <c r="G30">
+        <v>43.25</v>
+      </c>
+      <c r="H30">
+        <v>42.75</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>1069275</v>
+      </c>
+      <c r="L30">
+        <v>45962.1565</v>
+      </c>
+      <c r="M30">
+        <v>169400</v>
+      </c>
+      <c r="N30">
         <v>43</v>
       </c>
-      <c r="D30">
-        <v>0.75</v>
-      </c>
-      <c r="E30">
-        <v>1.7751479289940828</v>
-      </c>
-      <c r="F30">
-        <v>42.25</v>
-      </c>
-      <c r="G30">
-        <v>43</v>
-      </c>
-      <c r="H30">
-        <v>42.25</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>3416278</v>
-      </c>
-      <c r="L30">
-        <v>145375.28725</v>
-      </c>
-      <c r="M30">
-        <v>512400</v>
-      </c>
-      <c r="N30">
-        <v>42.75</v>
-      </c>
       <c r="O30">
-        <v>43</v>
+        <v>43.25</v>
       </c>
       <c r="P30">
-        <v>541100</v>
+        <v>433700</v>
       </c>
     </row>
     <row r="31">
@@ -1564,22 +1564,22 @@
         <v>-</v>
       </c>
       <c r="C31">
-        <v>56</v>
+        <v>57.75</v>
       </c>
       <c r="D31">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>5.164319248826291</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>53.5</v>
+        <v>57.75</v>
       </c>
       <c r="G31">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H31">
-        <v>53.5</v>
+        <v>57</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1588,22 +1588,22 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>13761685</v>
+        <v>3911064</v>
       </c>
       <c r="L31">
-        <v>760347.29625</v>
+        <v>224982.16525</v>
       </c>
       <c r="M31">
-        <v>470100</v>
+        <v>329900</v>
       </c>
       <c r="N31">
-        <v>55.75</v>
+        <v>57.5</v>
       </c>
       <c r="O31">
-        <v>56</v>
+        <v>57.75</v>
       </c>
       <c r="P31">
-        <v>1152400</v>
+        <v>218900</v>
       </c>
     </row>
     <row r="32">
@@ -1617,43 +1617,43 @@
         <v>339</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>0.8928571428571429</v>
+        <v>0.2958579881656805</v>
       </c>
       <c r="F32">
         <v>337</v>
       </c>
       <c r="G32">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H32">
         <v>337</v>
       </c>
       <c r="I32">
-        <v>383600</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>128889.6</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>1036991</v>
+        <v>1875224</v>
       </c>
       <c r="L32">
-        <v>350587.117</v>
+        <v>634175.786</v>
       </c>
       <c r="M32">
-        <v>80400</v>
+        <v>111400</v>
       </c>
       <c r="N32">
+        <v>338</v>
+      </c>
+      <c r="O32">
         <v>339</v>
       </c>
-      <c r="O32">
-        <v>340</v>
-      </c>
       <c r="P32">
-        <v>346400</v>
+        <v>98600</v>
       </c>
     </row>
     <row r="33">
@@ -1664,13 +1664,13 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>0.4132231404958678</v>
       </c>
       <c r="F33">
         <v>24.3</v>
@@ -1679,7 +1679,7 @@
         <v>24.4</v>
       </c>
       <c r="H33">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1688,22 +1688,22 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>5826301</v>
+        <v>1274520</v>
       </c>
       <c r="L33">
-        <v>140430.1129</v>
+        <v>30903.6704</v>
       </c>
       <c r="M33">
-        <v>456900</v>
+        <v>129900</v>
       </c>
       <c r="N33">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="O33">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="P33">
-        <v>334700</v>
+        <v>232900</v>
       </c>
     </row>
     <row r="34">
@@ -1714,37 +1714,37 @@
         <v>-</v>
       </c>
       <c r="C34">
+        <v>43</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
         <v>43.25</v>
       </c>
-      <c r="D34">
-        <v>0.5</v>
-      </c>
-      <c r="E34">
-        <v>1.1695906432748537</v>
-      </c>
-      <c r="F34">
+      <c r="G34">
+        <v>43.25</v>
+      </c>
+      <c r="H34">
         <v>43</v>
       </c>
-      <c r="G34">
-        <v>43.5</v>
-      </c>
-      <c r="H34">
-        <v>42.5</v>
-      </c>
       <c r="I34">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>21250</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>2620074</v>
+        <v>232742</v>
       </c>
       <c r="L34">
-        <v>112410.674</v>
+        <v>10038.92025</v>
       </c>
       <c r="M34">
-        <v>469900</v>
+        <v>263400</v>
       </c>
       <c r="N34">
         <v>43</v>
@@ -1753,7 +1753,7 @@
         <v>43.25</v>
       </c>
       <c r="P34">
-        <v>340500</v>
+        <v>266800</v>
       </c>
     </row>
     <row r="35">
@@ -1764,46 +1764,46 @@
         <v>-</v>
       </c>
       <c r="C35">
+        <v>4.16</v>
+      </c>
+      <c r="D35">
+        <v>-0.04</v>
+      </c>
+      <c r="E35">
+        <v>-0.9523809523809523</v>
+      </c>
+      <c r="F35">
+        <v>4.18</v>
+      </c>
+      <c r="G35">
+        <v>4.18</v>
+      </c>
+      <c r="H35">
         <v>4.14</v>
       </c>
-      <c r="D35">
-        <v>0.04</v>
-      </c>
-      <c r="E35">
-        <v>0.975609756097561</v>
-      </c>
-      <c r="F35">
-        <v>4.1</v>
-      </c>
-      <c r="G35">
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>3563910</v>
+      </c>
+      <c r="L35">
+        <v>14837.03822</v>
+      </c>
+      <c r="M35">
+        <v>922200</v>
+      </c>
+      <c r="N35">
         <v>4.14</v>
       </c>
-      <c r="H35">
-        <v>4.08</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>5713438</v>
-      </c>
-      <c r="L35">
-        <v>23519.06614</v>
-      </c>
-      <c r="M35">
-        <v>1390900</v>
-      </c>
-      <c r="N35">
-        <v>4.12</v>
-      </c>
       <c r="O35">
-        <v>4.14</v>
+        <v>4.16</v>
       </c>
       <c r="P35">
-        <v>3801400</v>
+        <v>445500</v>
       </c>
     </row>
     <row r="36">
@@ -1814,46 +1814,46 @@
         <v>-</v>
       </c>
       <c r="C36">
+        <v>101.5</v>
+      </c>
+      <c r="D36">
+        <v>-0.5</v>
+      </c>
+      <c r="E36">
+        <v>-0.49019607843137253</v>
+      </c>
+      <c r="F36">
+        <v>102</v>
+      </c>
+      <c r="G36">
         <v>102.5</v>
       </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>103</v>
-      </c>
-      <c r="G36">
-        <v>103</v>
-      </c>
       <c r="H36">
+        <v>101.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>806699</v>
+      </c>
+      <c r="L36">
+        <v>82012.9315</v>
+      </c>
+      <c r="M36">
+        <v>368100</v>
+      </c>
+      <c r="N36">
+        <v>101.5</v>
+      </c>
+      <c r="O36">
         <v>102</v>
       </c>
-      <c r="I36">
-        <v>80000</v>
-      </c>
-      <c r="J36">
-        <v>8200</v>
-      </c>
-      <c r="K36">
-        <v>1334395</v>
-      </c>
-      <c r="L36">
-        <v>136621.43</v>
-      </c>
-      <c r="M36">
-        <v>1074200</v>
-      </c>
-      <c r="N36">
-        <v>102</v>
-      </c>
-      <c r="O36">
-        <v>102.5</v>
-      </c>
       <c r="P36">
-        <v>744900</v>
+        <v>357500</v>
       </c>
     </row>
     <row r="37">
@@ -1864,22 +1864,22 @@
         <v>-</v>
       </c>
       <c r="C37">
+        <v>1.46</v>
+      </c>
+      <c r="D37">
+        <v>0.01</v>
+      </c>
+      <c r="E37">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="F37">
         <v>1.45</v>
       </c>
-      <c r="D37">
-        <v>-0.02</v>
-      </c>
-      <c r="E37">
-        <v>-1.3605442176870748</v>
-      </c>
-      <c r="F37">
-        <v>1.47</v>
-      </c>
       <c r="G37">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H37">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1888,13 +1888,13 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>169032790</v>
+        <v>125265315</v>
       </c>
       <c r="L37">
-        <v>247073.13209</v>
+        <v>181621.13614</v>
       </c>
       <c r="M37">
-        <v>64840300</v>
+        <v>9969700</v>
       </c>
       <c r="N37">
         <v>1.45</v>
@@ -1903,7 +1903,7 @@
         <v>1.46</v>
       </c>
       <c r="P37">
-        <v>14204100</v>
+        <v>66108700</v>
       </c>
     </row>
     <row r="38">
@@ -1914,22 +1914,22 @@
         <v>-</v>
       </c>
       <c r="C38">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="D38">
         <v>0.1</v>
       </c>
       <c r="E38">
-        <v>0.625</v>
+        <v>0.6211180124223602</v>
       </c>
       <c r="F38">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="G38">
         <v>16.2</v>
       </c>
       <c r="H38">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -1938,13 +1938,13 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>5753906</v>
+        <v>4613789</v>
       </c>
       <c r="L38">
-        <v>92544.43909999999</v>
+        <v>74294.3007</v>
       </c>
       <c r="M38">
-        <v>1999500</v>
+        <v>1120400</v>
       </c>
       <c r="N38">
         <v>16.1</v>
@@ -1953,7 +1953,7 @@
         <v>16.2</v>
       </c>
       <c r="P38">
-        <v>2365500</v>
+        <v>2225000</v>
       </c>
     </row>
     <row r="39">
@@ -1964,22 +1964,22 @@
         <v>-</v>
       </c>
       <c r="C39">
-        <v>3.86</v>
+        <v>3.98</v>
       </c>
       <c r="D39">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="E39">
-        <v>2.1164021164021163</v>
+        <v>-0.9950248756218906</v>
       </c>
       <c r="F39">
-        <v>3.82</v>
+        <v>4.02</v>
       </c>
       <c r="G39">
-        <v>3.88</v>
+        <v>4.02</v>
       </c>
       <c r="H39">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -1988,22 +1988,22 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>77437202</v>
+        <v>53274962</v>
       </c>
       <c r="L39">
-        <v>297193.25136</v>
+        <v>211880.63530000002</v>
       </c>
       <c r="M39">
-        <v>2703900</v>
+        <v>2979500</v>
       </c>
       <c r="N39">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="O39">
-        <v>3.86</v>
+        <v>3.98</v>
       </c>
       <c r="P39">
-        <v>8119300</v>
+        <v>2721100</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (3).xlsx
+++ b/Excel/StockQuotation (3).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>03/02/23 12:58:16</v>
+        <v>07/02/23 23:29:43</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1201.75</v>
+        <v>1191.42</v>
       </c>
       <c r="B7" t="str">
-        <v>-3.47 (-0.2879%)</v>
+        <v>-2.23 (-0.1868%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1205.23</v>
+        <v>1197.47</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1196.56</v>
+        <v>1187.34</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>435614522</v>
+        <v>698061801</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>8936784860.96</v>
+        <v>12747013905.25</v>
       </c>
     </row>
     <row r="9">
@@ -514,22 +514,22 @@
         <v>-</v>
       </c>
       <c r="C10">
+        <v>196.5</v>
+      </c>
+      <c r="D10">
+        <v>-0.5</v>
+      </c>
+      <c r="E10">
+        <v>-0.25380710659898476</v>
+      </c>
+      <c r="F10">
+        <v>197</v>
+      </c>
+      <c r="G10">
         <v>198</v>
       </c>
-      <c r="D10">
-        <v>0.5</v>
-      </c>
-      <c r="E10">
-        <v>0.25316455696202533</v>
-      </c>
-      <c r="F10">
-        <v>197.5</v>
-      </c>
-      <c r="G10">
-        <v>198.5</v>
-      </c>
       <c r="H10">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -538,22 +538,22 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>926679</v>
+        <v>3223977</v>
       </c>
       <c r="L10">
-        <v>183244.338</v>
+        <v>633905.6665</v>
       </c>
       <c r="M10">
-        <v>127900</v>
+        <v>581100</v>
       </c>
       <c r="N10">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O10">
-        <v>198.5</v>
+        <v>196.5</v>
       </c>
       <c r="P10">
-        <v>132800</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="11">
@@ -564,46 +564,46 @@
         <v>-</v>
       </c>
       <c r="C11">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="D11">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E11">
-        <v>-1.639344262295082</v>
+        <v>0.847457627118644</v>
       </c>
       <c r="F11">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="G11">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="H11">
+        <v>11.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>16341272</v>
+      </c>
+      <c r="L11">
+        <v>193278.3275</v>
+      </c>
+      <c r="M11">
+        <v>2417300</v>
+      </c>
+      <c r="N11">
         <v>11.8</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>18412971</v>
-      </c>
-      <c r="L11">
-        <v>220380.516</v>
-      </c>
-      <c r="M11">
-        <v>287400</v>
-      </c>
-      <c r="N11">
-        <v>12</v>
-      </c>
       <c r="O11">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="P11">
-        <v>1609600</v>
+        <v>754800</v>
       </c>
     </row>
     <row r="12">
@@ -614,22 +614,22 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>161.5</v>
+        <v>160.5</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>-0.3105590062111801</v>
       </c>
       <c r="F12">
         <v>161.5</v>
       </c>
       <c r="G12">
-        <v>162</v>
+        <v>161.5</v>
       </c>
       <c r="H12">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -638,22 +638,22 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>2211193</v>
+        <v>3101777</v>
       </c>
       <c r="L12">
-        <v>356945.837</v>
+        <v>497468.5115</v>
       </c>
       <c r="M12">
-        <v>328100</v>
+        <v>756800</v>
       </c>
       <c r="N12">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O12">
-        <v>161.5</v>
+        <v>160.5</v>
       </c>
       <c r="P12">
-        <v>159400</v>
+        <v>235000</v>
       </c>
     </row>
     <row r="13">
@@ -664,22 +664,22 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="D13">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E13">
-        <v>0.9345794392523364</v>
+        <v>-0.9389671361502347</v>
       </c>
       <c r="F13">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="G13">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="H13">
-        <v>21.4</v>
+        <v>20.9</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -688,22 +688,22 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>6836436</v>
+        <v>11021734</v>
       </c>
       <c r="L13">
-        <v>147330.1925</v>
+        <v>232419.2244</v>
       </c>
       <c r="M13">
-        <v>853900</v>
+        <v>2048300</v>
       </c>
       <c r="N13">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="O13">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="P13">
-        <v>289200</v>
+        <v>189800</v>
       </c>
     </row>
     <row r="14">
@@ -717,10 +717,10 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>-0.9900990099009901</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>10.1</v>
@@ -729,7 +729,7 @@
         <v>10.1</v>
       </c>
       <c r="H14">
-        <v>9.95</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -738,22 +738,22 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>1716422</v>
+        <v>1404493</v>
       </c>
       <c r="L14">
-        <v>17156.9141</v>
+        <v>14074.1795</v>
       </c>
       <c r="M14">
-        <v>679000</v>
+        <v>640200</v>
       </c>
       <c r="N14">
-        <v>9.95</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="P14">
-        <v>413600</v>
+        <v>895700</v>
       </c>
     </row>
     <row r="15">
@@ -764,22 +764,22 @@
         <v>-</v>
       </c>
       <c r="C15">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="D15">
         <v>-0.05</v>
       </c>
       <c r="E15">
-        <v>-0.591715976331361</v>
+        <v>-0.6024096385542169</v>
       </c>
       <c r="F15">
+        <v>8.3</v>
+      </c>
+      <c r="G15">
         <v>8.4</v>
       </c>
-      <c r="G15">
-        <v>8.45</v>
-      </c>
       <c r="H15">
-        <v>8.4</v>
+        <v>8.2</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -788,22 +788,22 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>6616794</v>
+        <v>52782066</v>
       </c>
       <c r="L15">
-        <v>55847.0761</v>
+        <v>436595.46095</v>
       </c>
       <c r="M15">
-        <v>5078500</v>
+        <v>267700</v>
       </c>
       <c r="N15">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="O15">
-        <v>8.45</v>
+        <v>8.3</v>
       </c>
       <c r="P15">
-        <v>1630800</v>
+        <v>1769900</v>
       </c>
     </row>
     <row r="16">
@@ -814,46 +814,46 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="D16">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="E16">
-        <v>-2.985074626865672</v>
+        <v>-1.0204081632653061</v>
       </c>
       <c r="F16">
-        <v>4.02</v>
+        <v>3.92</v>
       </c>
       <c r="G16">
-        <v>4.02</v>
+        <v>3.92</v>
       </c>
       <c r="H16">
+        <v>3.84</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>34601807</v>
+      </c>
+      <c r="L16">
+        <v>133738.43502</v>
+      </c>
+      <c r="M16">
+        <v>1579900</v>
+      </c>
+      <c r="N16">
         <v>3.86</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>65572992</v>
-      </c>
-      <c r="L16">
-        <v>257050.73036000002</v>
-      </c>
-      <c r="M16">
-        <v>1628200</v>
-      </c>
-      <c r="N16">
+      <c r="O16">
         <v>3.88</v>
       </c>
-      <c r="O16">
-        <v>3.9</v>
-      </c>
       <c r="P16">
-        <v>2800600</v>
+        <v>1263300</v>
       </c>
     </row>
     <row r="17">
@@ -864,7 +864,7 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -873,13 +873,13 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="G17">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="H17">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -888,22 +888,22 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>9578760</v>
+        <v>17028962</v>
       </c>
       <c r="L17">
-        <v>228593.6587</v>
+        <v>401183.07739999995</v>
       </c>
       <c r="M17">
-        <v>1523800</v>
+        <v>2056100</v>
       </c>
       <c r="N17">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="O17">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="P17">
-        <v>474400</v>
+        <v>347500</v>
       </c>
     </row>
     <row r="18">
@@ -914,22 +914,22 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>173.5</v>
+        <v>172</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="E18">
-        <v>-0.5730659025787965</v>
+        <v>-0.2898550724637681</v>
       </c>
       <c r="F18">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G18">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H18">
-        <v>173.5</v>
+        <v>171</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -938,22 +938,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>254316</v>
+        <v>944769</v>
       </c>
       <c r="L18">
-        <v>44194.1755</v>
+        <v>162568.3245</v>
       </c>
       <c r="M18">
-        <v>52200</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>173.5</v>
+        <v>172</v>
       </c>
       <c r="O18">
-        <v>174</v>
+        <v>172.5</v>
       </c>
       <c r="P18">
-        <v>58700</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="19">
@@ -964,46 +964,46 @@
         <v>-</v>
       </c>
       <c r="C19">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="D19">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="E19">
-        <v>-0.4</v>
+        <v>-0.8032128514056225</v>
       </c>
       <c r="F19">
         <v>5</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="H19">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>580000</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>2865.2</v>
       </c>
       <c r="K19">
-        <v>3485277</v>
+        <v>52248036</v>
       </c>
       <c r="L19">
-        <v>17380.11324</v>
+        <v>259856.6892</v>
       </c>
       <c r="M19">
-        <v>4818900</v>
+        <v>7270900</v>
       </c>
       <c r="N19">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="O19">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="P19">
-        <v>3493200</v>
+        <v>43100</v>
       </c>
     </row>
     <row r="20">
@@ -1017,34 +1017,34 @@
         <v>64</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>0.75</v>
       </c>
       <c r="E20">
-        <v>-1.5384615384615385</v>
+        <v>1.1857707509881423</v>
       </c>
       <c r="F20">
-        <v>64.5</v>
+        <v>63</v>
       </c>
       <c r="G20">
         <v>65</v>
       </c>
       <c r="H20">
-        <v>63.75</v>
+        <v>63</v>
       </c>
       <c r="I20">
-        <v>154800</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>10017.94392</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>8214450</v>
+        <v>14815331</v>
       </c>
       <c r="L20">
-        <v>528159.57017</v>
+        <v>949666.43975</v>
       </c>
       <c r="M20">
-        <v>125100</v>
+        <v>274800</v>
       </c>
       <c r="N20">
         <v>64</v>
@@ -1053,7 +1053,7 @@
         <v>64.25</v>
       </c>
       <c r="P20">
-        <v>90600</v>
+        <v>258800</v>
       </c>
     </row>
     <row r="21">
@@ -1064,46 +1064,46 @@
         <v>-</v>
       </c>
       <c r="C21">
-        <v>73.5</v>
+        <v>72.5</v>
       </c>
       <c r="D21">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E21">
-        <v>0.684931506849315</v>
+        <v>-0.3436426116838488</v>
       </c>
       <c r="F21">
         <v>72.75</v>
       </c>
       <c r="G21">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H21">
+        <v>72.25</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>1572591</v>
+      </c>
+      <c r="L21">
+        <v>114134.26675</v>
+      </c>
+      <c r="M21">
+        <v>25400</v>
+      </c>
+      <c r="N21">
+        <v>72.5</v>
+      </c>
+      <c r="O21">
         <v>72.75</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>802203</v>
-      </c>
-      <c r="L21">
-        <v>58812.5405</v>
-      </c>
-      <c r="M21">
-        <v>85100</v>
-      </c>
-      <c r="N21">
-        <v>73.25</v>
-      </c>
-      <c r="O21">
-        <v>73.5</v>
-      </c>
       <c r="P21">
-        <v>37400</v>
+        <v>154600</v>
       </c>
     </row>
     <row r="22">
@@ -1114,46 +1114,46 @@
         <v>-</v>
       </c>
       <c r="C22">
-        <v>68</v>
+        <v>67.5</v>
       </c>
       <c r="D22">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="E22">
-        <v>-0.7299270072992701</v>
+        <v>-1.4598540145985401</v>
       </c>
       <c r="F22">
-        <v>68.75</v>
+        <v>68.5</v>
       </c>
       <c r="G22">
-        <v>68.75</v>
+        <v>68.5</v>
       </c>
       <c r="H22">
-        <v>68</v>
+        <v>67.25</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>40500</v>
       </c>
       <c r="K22">
-        <v>3221568</v>
+        <v>9986259</v>
       </c>
       <c r="L22">
-        <v>220126.521</v>
+        <v>675593.27775</v>
       </c>
       <c r="M22">
-        <v>1284000</v>
+        <v>688400</v>
       </c>
       <c r="N22">
-        <v>68</v>
+        <v>67.25</v>
       </c>
       <c r="O22">
-        <v>68.25</v>
+        <v>67.5</v>
       </c>
       <c r="P22">
-        <v>311600</v>
+        <v>110400</v>
       </c>
     </row>
     <row r="23">
@@ -1164,22 +1164,22 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="D23">
         <v>-0.2</v>
       </c>
       <c r="E23">
-        <v>-1.1299435028248588</v>
+        <v>-1.1494252873563218</v>
       </c>
       <c r="F23">
-        <v>17.7</v>
+        <v>17.3</v>
       </c>
       <c r="G23">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="H23">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1188,22 +1188,22 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>8304490</v>
+        <v>37917040</v>
       </c>
       <c r="L23">
-        <v>146039.773</v>
+        <v>654660.8281</v>
       </c>
       <c r="M23">
-        <v>9742600</v>
+        <v>6309000</v>
       </c>
       <c r="N23">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="O23">
-        <v>17.6</v>
+        <v>17.3</v>
       </c>
       <c r="P23">
-        <v>1840600</v>
+        <v>3186300</v>
       </c>
     </row>
     <row r="24">
@@ -1217,16 +1217,16 @@
         <v>9.9</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>0.5076142131979695</v>
       </c>
       <c r="F24">
         <v>9.9</v>
       </c>
       <c r="G24">
-        <v>9.95</v>
+        <v>9.9</v>
       </c>
       <c r="H24">
         <v>9.8</v>
@@ -1238,22 +1238,22 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>23912903</v>
+        <v>17389859</v>
       </c>
       <c r="L24">
-        <v>236162.3487</v>
+        <v>171529.96815</v>
       </c>
       <c r="M24">
-        <v>947900</v>
+        <v>2477700</v>
       </c>
       <c r="N24">
+        <v>9.85</v>
+      </c>
+      <c r="O24">
         <v>9.9</v>
       </c>
-      <c r="O24">
-        <v>9.95</v>
-      </c>
       <c r="P24">
-        <v>6180400</v>
+        <v>4248600</v>
       </c>
     </row>
     <row r="25">
@@ -1264,22 +1264,22 @@
         <v>-</v>
       </c>
       <c r="C25">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="D25">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="G25">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="H25">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1288,22 +1288,22 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>2285421</v>
+        <v>8430180</v>
       </c>
       <c r="L25">
-        <v>27429.3772</v>
+        <v>98138.46029999999</v>
       </c>
       <c r="M25">
-        <v>358100</v>
+        <v>115300</v>
       </c>
       <c r="N25">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="O25">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="P25">
-        <v>1005200</v>
+        <v>439100</v>
       </c>
     </row>
     <row r="26">
@@ -1314,13 +1314,13 @@
         <v>-</v>
       </c>
       <c r="C26">
-        <v>28.25</v>
+        <v>28.5</v>
       </c>
       <c r="D26">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="E26">
-        <v>-0.8771929824561403</v>
+        <v>0.8849557522123894</v>
       </c>
       <c r="F26">
         <v>28.25</v>
@@ -1329,7 +1329,7 @@
         <v>28.5</v>
       </c>
       <c r="H26">
-        <v>28.25</v>
+        <v>28</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>1108746</v>
+        <v>5471542</v>
       </c>
       <c r="L26">
-        <v>31330.526</v>
+        <v>154774.204</v>
       </c>
       <c r="M26">
-        <v>639800</v>
+        <v>760700</v>
       </c>
       <c r="N26">
         <v>28.25</v>
@@ -1353,7 +1353,7 @@
         <v>28.5</v>
       </c>
       <c r="P26">
-        <v>1398300</v>
+        <v>714100</v>
       </c>
     </row>
     <row r="27">
@@ -1364,16 +1364,16 @@
         <v>-</v>
       </c>
       <c r="C27">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>-0.7633587786259542</v>
       </c>
       <c r="F27">
-        <v>33</v>
+        <v>32.75</v>
       </c>
       <c r="G27">
         <v>33</v>
@@ -1388,22 +1388,22 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>37092275</v>
+        <v>33729036</v>
       </c>
       <c r="L27">
-        <v>1217492.49675</v>
+        <v>1100507.0125</v>
       </c>
       <c r="M27">
-        <v>13678200</v>
+        <v>13937300</v>
       </c>
       <c r="N27">
+        <v>32.5</v>
+      </c>
+      <c r="O27">
         <v>32.75</v>
       </c>
-      <c r="O27">
-        <v>33</v>
-      </c>
       <c r="P27">
-        <v>10779800</v>
+        <v>1785800</v>
       </c>
     </row>
     <row r="28">
@@ -1414,46 +1414,46 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D28">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>-2.3529411764705883</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="F28">
-        <v>169.5</v>
+        <v>164</v>
       </c>
       <c r="G28">
-        <v>169.5</v>
+        <v>165.5</v>
       </c>
       <c r="H28">
+        <v>164</v>
+      </c>
+      <c r="I28">
+        <v>160000</v>
+      </c>
+      <c r="J28">
+        <v>26240</v>
+      </c>
+      <c r="K28">
+        <v>15544249</v>
+      </c>
+      <c r="L28">
+        <v>2560725.5295</v>
+      </c>
+      <c r="M28">
+        <v>810500</v>
+      </c>
+      <c r="N28">
         <v>164.5</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>20392736</v>
-      </c>
-      <c r="L28">
-        <v>3387949.05</v>
-      </c>
-      <c r="M28">
-        <v>773000</v>
-      </c>
-      <c r="N28">
-        <v>166</v>
-      </c>
       <c r="O28">
-        <v>166.5</v>
+        <v>165</v>
       </c>
       <c r="P28">
-        <v>252600</v>
+        <v>30300</v>
       </c>
     </row>
     <row r="29">
@@ -1464,7 +1464,7 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G29">
         <v>2.38</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>18778190</v>
+        <v>20156462</v>
       </c>
       <c r="L29">
-        <v>44348.56588</v>
+        <v>47521.32348</v>
       </c>
       <c r="M29">
-        <v>1974200</v>
+        <v>521800</v>
       </c>
       <c r="N29">
         <v>2.36</v>
@@ -1503,7 +1503,7 @@
         <v>2.38</v>
       </c>
       <c r="P29">
-        <v>13838000</v>
+        <v>7927400</v>
       </c>
     </row>
     <row r="30">
@@ -1514,46 +1514,46 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>43.25</v>
+        <v>42.5</v>
       </c>
       <c r="D30">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="E30">
-        <v>0.5813953488372093</v>
+        <v>-0.5847953216374269</v>
       </c>
       <c r="F30">
+        <v>42.5</v>
+      </c>
+      <c r="G30">
         <v>42.75</v>
       </c>
-      <c r="G30">
-        <v>43.25</v>
-      </c>
       <c r="H30">
+        <v>42.25</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>2231778</v>
+      </c>
+      <c r="L30">
+        <v>94917.6095</v>
+      </c>
+      <c r="M30">
+        <v>242100</v>
+      </c>
+      <c r="N30">
+        <v>42.5</v>
+      </c>
+      <c r="O30">
         <v>42.75</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>1069275</v>
-      </c>
-      <c r="L30">
-        <v>45962.1565</v>
-      </c>
-      <c r="M30">
-        <v>169400</v>
-      </c>
-      <c r="N30">
-        <v>43</v>
-      </c>
-      <c r="O30">
-        <v>43.25</v>
-      </c>
       <c r="P30">
-        <v>433700</v>
+        <v>159700</v>
       </c>
     </row>
     <row r="31">
@@ -1564,22 +1564,22 @@
         <v>-</v>
       </c>
       <c r="C31">
-        <v>57.75</v>
+        <v>55.5</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>-1.7699115044247788</v>
       </c>
       <c r="F31">
-        <v>57.75</v>
+        <v>56</v>
       </c>
       <c r="G31">
-        <v>58</v>
+        <v>56.5</v>
       </c>
       <c r="H31">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1588,22 +1588,22 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>3911064</v>
+        <v>10005330</v>
       </c>
       <c r="L31">
-        <v>224982.16525</v>
+        <v>555531.02575</v>
       </c>
       <c r="M31">
-        <v>329900</v>
+        <v>289500</v>
       </c>
       <c r="N31">
-        <v>57.5</v>
+        <v>55.25</v>
       </c>
       <c r="O31">
-        <v>57.75</v>
+        <v>55.5</v>
       </c>
       <c r="P31">
-        <v>218900</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="32">
@@ -1614,46 +1614,46 @@
         <v>-</v>
       </c>
       <c r="C32">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <v>0.2958579881656805</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="F32">
         <v>337</v>
       </c>
       <c r="G32">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H32">
+        <v>336</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>2304687</v>
+      </c>
+      <c r="L32">
+        <v>778502.554</v>
+      </c>
+      <c r="M32">
+        <v>487000</v>
+      </c>
+      <c r="N32">
         <v>337</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>1875224</v>
-      </c>
-      <c r="L32">
-        <v>634175.786</v>
-      </c>
-      <c r="M32">
-        <v>111400</v>
-      </c>
-      <c r="N32">
+      <c r="O32">
         <v>338</v>
       </c>
-      <c r="O32">
-        <v>339</v>
-      </c>
       <c r="P32">
-        <v>98600</v>
+        <v>211800</v>
       </c>
     </row>
     <row r="33">
@@ -1664,19 +1664,19 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="D33">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E33">
-        <v>0.4132231404958678</v>
+        <v>1.2396694214876034</v>
       </c>
       <c r="F33">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="G33">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="H33">
         <v>24.1</v>
@@ -1688,22 +1688,22 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>1274520</v>
+        <v>17117094</v>
       </c>
       <c r="L33">
-        <v>30903.6704</v>
+        <v>418845.7735</v>
       </c>
       <c r="M33">
-        <v>129900</v>
+        <v>443500</v>
       </c>
       <c r="N33">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="O33">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="P33">
-        <v>232900</v>
+        <v>289200</v>
       </c>
     </row>
     <row r="34">
@@ -1714,22 +1714,22 @@
         <v>-</v>
       </c>
       <c r="C34">
+        <v>43.25</v>
+      </c>
+      <c r="D34">
+        <v>0.25</v>
+      </c>
+      <c r="E34">
+        <v>0.5813953488372093</v>
+      </c>
+      <c r="F34">
         <v>43</v>
       </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>43.25</v>
-      </c>
       <c r="G34">
-        <v>43.25</v>
+        <v>43.5</v>
       </c>
       <c r="H34">
-        <v>43</v>
+        <v>42.75</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1738,13 +1738,13 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>232742</v>
+        <v>1622069</v>
       </c>
       <c r="L34">
-        <v>10038.92025</v>
+        <v>69930.36075</v>
       </c>
       <c r="M34">
-        <v>263400</v>
+        <v>325300</v>
       </c>
       <c r="N34">
         <v>43</v>
@@ -1753,7 +1753,7 @@
         <v>43.25</v>
       </c>
       <c r="P34">
-        <v>266800</v>
+        <v>298900</v>
       </c>
     </row>
     <row r="35">
@@ -1764,22 +1764,22 @@
         <v>-</v>
       </c>
       <c r="C35">
-        <v>4.16</v>
+        <v>4.06</v>
       </c>
       <c r="D35">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E35">
-        <v>-0.9523809523809523</v>
+        <v>-1.4563106796116505</v>
       </c>
       <c r="F35">
-        <v>4.18</v>
+        <v>4.1</v>
       </c>
       <c r="G35">
-        <v>4.18</v>
+        <v>4.12</v>
       </c>
       <c r="H35">
-        <v>4.14</v>
+        <v>4.06</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1788,22 +1788,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>3563910</v>
+        <v>18301546</v>
       </c>
       <c r="L35">
-        <v>14837.03822</v>
+        <v>74524.31034</v>
       </c>
       <c r="M35">
-        <v>922200</v>
+        <v>2654200</v>
       </c>
       <c r="N35">
-        <v>4.14</v>
+        <v>4.06</v>
       </c>
       <c r="O35">
-        <v>4.16</v>
+        <v>4.08</v>
       </c>
       <c r="P35">
-        <v>445500</v>
+        <v>499100</v>
       </c>
     </row>
     <row r="36">
@@ -1814,46 +1814,46 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="D36">
         <v>-0.5</v>
       </c>
       <c r="E36">
-        <v>-0.49019607843137253</v>
+        <v>-0.4854368932038835</v>
       </c>
       <c r="F36">
+        <v>103</v>
+      </c>
+      <c r="G36">
+        <v>103</v>
+      </c>
+      <c r="H36">
         <v>102</v>
       </c>
-      <c r="G36">
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>3757061</v>
+      </c>
+      <c r="L36">
+        <v>385313.0485</v>
+      </c>
+      <c r="M36">
+        <v>312300</v>
+      </c>
+      <c r="N36">
         <v>102.5</v>
       </c>
-      <c r="H36">
-        <v>101.5</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>806699</v>
-      </c>
-      <c r="L36">
-        <v>82012.9315</v>
-      </c>
-      <c r="M36">
-        <v>368100</v>
-      </c>
-      <c r="N36">
-        <v>101.5</v>
-      </c>
       <c r="O36">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P36">
-        <v>357500</v>
+        <v>1323400</v>
       </c>
     </row>
     <row r="37">
@@ -1864,22 +1864,22 @@
         <v>-</v>
       </c>
       <c r="C37">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="D37">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E37">
-        <v>0.6896551724137931</v>
+        <v>-2.0689655172413794</v>
       </c>
       <c r="F37">
+        <v>1.44</v>
+      </c>
+      <c r="G37">
         <v>1.45</v>
       </c>
-      <c r="G37">
-        <v>1.46</v>
-      </c>
       <c r="H37">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>125265315</v>
+        <v>194236716</v>
       </c>
       <c r="L37">
-        <v>181621.13614</v>
+        <v>276844.8389</v>
       </c>
       <c r="M37">
-        <v>9969700</v>
+        <v>17077300</v>
       </c>
       <c r="N37">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="O37">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P37">
-        <v>66108700</v>
+        <v>21403900</v>
       </c>
     </row>
     <row r="38">
@@ -1917,43 +1917,43 @@
         <v>16.2</v>
       </c>
       <c r="D38">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>0.6211180124223602</v>
+        <v>0</v>
       </c>
       <c r="F38">
+        <v>16.3</v>
+      </c>
+      <c r="G38">
+        <v>16.4</v>
+      </c>
+      <c r="H38">
         <v>16.1</v>
       </c>
-      <c r="G38">
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>16289493</v>
+      </c>
+      <c r="L38">
+        <v>264277.7181</v>
+      </c>
+      <c r="M38">
+        <v>1328900</v>
+      </c>
+      <c r="N38">
         <v>16.2</v>
       </c>
-      <c r="H38">
-        <v>16</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>4613789</v>
-      </c>
-      <c r="L38">
-        <v>74294.3007</v>
-      </c>
-      <c r="M38">
-        <v>1120400</v>
-      </c>
-      <c r="N38">
-        <v>16.1</v>
-      </c>
       <c r="O38">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P38">
-        <v>2225000</v>
+        <v>1582700</v>
       </c>
     </row>
     <row r="39">
@@ -1964,22 +1964,22 @@
         <v>-</v>
       </c>
       <c r="C39">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="D39">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E39">
-        <v>-0.9950248756218906</v>
+        <v>-0.5102040816326531</v>
       </c>
       <c r="F39">
-        <v>4.02</v>
+        <v>3.92</v>
       </c>
       <c r="G39">
-        <v>4.02</v>
+        <v>3.94</v>
       </c>
       <c r="H39">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -1988,22 +1988,22 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>53274962</v>
+        <v>73616885</v>
       </c>
       <c r="L39">
-        <v>211880.63530000002</v>
+        <v>286207.30916</v>
       </c>
       <c r="M39">
-        <v>2979500</v>
+        <v>6303600</v>
       </c>
       <c r="N39">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="O39">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="P39">
-        <v>2721100</v>
+        <v>1586700</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (3).xlsx
+++ b/Excel/StockQuotation (3).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>07/02/23 23:29:43</v>
+        <v>08/02/23 20:05:49</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1191.42</v>
+        <v>1186.79</v>
       </c>
       <c r="B7" t="str">
-        <v>-2.23 (-0.1868%)</v>
+        <v>-4.63 (-0.3886%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1197.47</v>
+        <v>1195.51</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1187.34</v>
+        <v>1184.27</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>698061801</v>
+        <v>686914081</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>12747013905.25</v>
+        <v>12259192408.05</v>
       </c>
     </row>
     <row r="9">
@@ -514,22 +514,22 @@
         <v>-</v>
       </c>
       <c r="C10">
+        <v>195.5</v>
+      </c>
+      <c r="D10">
+        <v>-1</v>
+      </c>
+      <c r="E10">
+        <v>-0.5089058524173028</v>
+      </c>
+      <c r="F10">
+        <v>196</v>
+      </c>
+      <c r="G10">
         <v>196.5</v>
       </c>
-      <c r="D10">
-        <v>-0.5</v>
-      </c>
-      <c r="E10">
-        <v>-0.25380710659898476</v>
-      </c>
-      <c r="F10">
-        <v>197</v>
-      </c>
-      <c r="G10">
-        <v>198</v>
-      </c>
       <c r="H10">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -538,22 +538,22 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3223977</v>
+        <v>3770659</v>
       </c>
       <c r="L10">
-        <v>633905.6665</v>
+        <v>737590.8815</v>
       </c>
       <c r="M10">
-        <v>581100</v>
+        <v>1010400</v>
       </c>
       <c r="N10">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O10">
-        <v>196.5</v>
+        <v>195.5</v>
       </c>
       <c r="P10">
-        <v>51200</v>
+        <v>235500</v>
       </c>
     </row>
     <row r="11">
@@ -567,43 +567,43 @@
         <v>11.9</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.847457627118644</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>11.9</v>
       </c>
       <c r="G11">
+        <v>12.1</v>
+      </c>
+      <c r="H11">
+        <v>11.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>23221669</v>
+      </c>
+      <c r="L11">
+        <v>277018.21280000004</v>
+      </c>
+      <c r="M11">
+        <v>675500</v>
+      </c>
+      <c r="N11">
         <v>11.9</v>
       </c>
-      <c r="H11">
-        <v>11.7</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>16341272</v>
-      </c>
-      <c r="L11">
-        <v>193278.3275</v>
-      </c>
-      <c r="M11">
-        <v>2417300</v>
-      </c>
-      <c r="N11">
-        <v>11.8</v>
-      </c>
       <c r="O11">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="P11">
-        <v>754800</v>
+        <v>4210700</v>
       </c>
     </row>
     <row r="12">
@@ -614,37 +614,37 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>160.5</v>
+        <v>160</v>
       </c>
       <c r="D12">
         <v>-0.5</v>
       </c>
       <c r="E12">
-        <v>-0.3105590062111801</v>
+        <v>-0.3115264797507788</v>
       </c>
       <c r="F12">
-        <v>161.5</v>
+        <v>160</v>
       </c>
       <c r="G12">
-        <v>161.5</v>
+        <v>161</v>
       </c>
       <c r="H12">
         <v>160</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>25680</v>
       </c>
       <c r="K12">
-        <v>3101777</v>
+        <v>3694629</v>
       </c>
       <c r="L12">
-        <v>497468.5115</v>
+        <v>592696.122</v>
       </c>
       <c r="M12">
-        <v>756800</v>
+        <v>505300</v>
       </c>
       <c r="N12">
         <v>160</v>
@@ -653,7 +653,7 @@
         <v>160.5</v>
       </c>
       <c r="P12">
-        <v>235000</v>
+        <v>189400</v>
       </c>
     </row>
     <row r="13">
@@ -664,19 +664,19 @@
         <v>-</v>
       </c>
       <c r="C13">
+        <v>21</v>
+      </c>
+      <c r="D13">
+        <v>-0.1</v>
+      </c>
+      <c r="E13">
+        <v>-0.47393364928909953</v>
+      </c>
+      <c r="F13">
         <v>21.1</v>
       </c>
-      <c r="D13">
-        <v>-0.2</v>
-      </c>
-      <c r="E13">
-        <v>-0.9389671361502347</v>
-      </c>
-      <c r="F13">
-        <v>21.3</v>
-      </c>
       <c r="G13">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="H13">
         <v>20.9</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>11021734</v>
+        <v>3154617</v>
       </c>
       <c r="L13">
-        <v>232419.2244</v>
+        <v>66212.80129999999</v>
       </c>
       <c r="M13">
-        <v>2048300</v>
+        <v>962800</v>
       </c>
       <c r="N13">
         <v>21</v>
@@ -703,7 +703,7 @@
         <v>21.1</v>
       </c>
       <c r="P13">
-        <v>189800</v>
+        <v>261500</v>
       </c>
     </row>
     <row r="14">
@@ -723,37 +723,37 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>10.1</v>
       </c>
       <c r="H14">
+        <v>9.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>2617235</v>
+      </c>
+      <c r="L14">
+        <v>26131.1178</v>
+      </c>
+      <c r="M14">
+        <v>102800</v>
+      </c>
+      <c r="N14">
+        <v>9.95</v>
+      </c>
+      <c r="O14">
         <v>10</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>1404493</v>
-      </c>
-      <c r="L14">
-        <v>14074.1795</v>
-      </c>
-      <c r="M14">
-        <v>640200</v>
-      </c>
-      <c r="N14">
-        <v>10</v>
-      </c>
-      <c r="O14">
-        <v>10.1</v>
-      </c>
       <c r="P14">
-        <v>895700</v>
+        <v>137100</v>
       </c>
     </row>
     <row r="15">
@@ -764,19 +764,19 @@
         <v>-</v>
       </c>
       <c r="C15">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
       <c r="D15">
         <v>-0.05</v>
       </c>
       <c r="E15">
-        <v>-0.6024096385542169</v>
+        <v>-0.6060606060606061</v>
       </c>
       <c r="F15">
         <v>8.3</v>
       </c>
       <c r="G15">
-        <v>8.4</v>
+        <v>8.3</v>
       </c>
       <c r="H15">
         <v>8.2</v>
@@ -788,22 +788,22 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>52782066</v>
+        <v>23116540</v>
       </c>
       <c r="L15">
-        <v>436595.46095</v>
+        <v>190510.177</v>
       </c>
       <c r="M15">
-        <v>267700</v>
+        <v>6632600</v>
       </c>
       <c r="N15">
+        <v>8.2</v>
+      </c>
+      <c r="O15">
         <v>8.25</v>
       </c>
-      <c r="O15">
-        <v>8.3</v>
-      </c>
       <c r="P15">
-        <v>1769900</v>
+        <v>1478800</v>
       </c>
     </row>
     <row r="16">
@@ -814,46 +814,46 @@
         <v>-</v>
       </c>
       <c r="C16">
+        <v>3.86</v>
+      </c>
+      <c r="D16">
+        <v>-0.02</v>
+      </c>
+      <c r="E16">
+        <v>-0.5154639175257731</v>
+      </c>
+      <c r="F16">
         <v>3.88</v>
       </c>
-      <c r="D16">
-        <v>-0.04</v>
-      </c>
-      <c r="E16">
-        <v>-1.0204081632653061</v>
-      </c>
-      <c r="F16">
-        <v>3.92</v>
-      </c>
       <c r="G16">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="H16">
+        <v>3.82</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>15465710</v>
+      </c>
+      <c r="L16">
+        <v>59680.096979999995</v>
+      </c>
+      <c r="M16">
+        <v>962000</v>
+      </c>
+      <c r="N16">
         <v>3.84</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>34601807</v>
-      </c>
-      <c r="L16">
-        <v>133738.43502</v>
-      </c>
-      <c r="M16">
-        <v>1579900</v>
-      </c>
-      <c r="N16">
+      <c r="O16">
         <v>3.86</v>
       </c>
-      <c r="O16">
-        <v>3.88</v>
-      </c>
       <c r="P16">
-        <v>1263300</v>
+        <v>654700</v>
       </c>
     </row>
     <row r="17">
@@ -864,46 +864,46 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>-1.271186440677966</v>
       </c>
       <c r="F17">
         <v>23.6</v>
       </c>
       <c r="G17">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="H17">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>3472000</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>80897.6</v>
       </c>
       <c r="K17">
-        <v>17028962</v>
+        <v>28889712</v>
       </c>
       <c r="L17">
-        <v>401183.07739999995</v>
+        <v>675575.3047999999</v>
       </c>
       <c r="M17">
-        <v>2056100</v>
+        <v>5431700</v>
       </c>
       <c r="N17">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="O17">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="P17">
-        <v>347500</v>
+        <v>1514900</v>
       </c>
     </row>
     <row r="18">
@@ -914,13 +914,13 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>172</v>
+        <v>171.5</v>
       </c>
       <c r="D18">
         <v>-0.5</v>
       </c>
       <c r="E18">
-        <v>-0.2898550724637681</v>
+        <v>-0.29069767441860467</v>
       </c>
       <c r="F18">
         <v>172</v>
@@ -938,22 +938,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>944769</v>
+        <v>642855</v>
       </c>
       <c r="L18">
-        <v>162568.3245</v>
+        <v>110252.033</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>10100</v>
       </c>
       <c r="N18">
+        <v>171.5</v>
+      </c>
+      <c r="O18">
         <v>172</v>
       </c>
-      <c r="O18">
-        <v>172.5</v>
-      </c>
       <c r="P18">
-        <v>23000</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="19">
@@ -964,46 +964,46 @@
         <v>-</v>
       </c>
       <c r="C19">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="D19">
         <v>-0.04</v>
       </c>
       <c r="E19">
-        <v>-0.8032128514056225</v>
+        <v>-0.8097165991902834</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="G19">
-        <v>5.05</v>
+        <v>4.98</v>
       </c>
       <c r="H19">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="I19">
-        <v>580000</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>2865.2</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>52248036</v>
+        <v>83042776</v>
       </c>
       <c r="L19">
-        <v>259856.6892</v>
+        <v>409026.96532</v>
       </c>
       <c r="M19">
-        <v>7270900</v>
+        <v>6304200</v>
       </c>
       <c r="N19">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="O19">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="P19">
-        <v>43100</v>
+        <v>621200</v>
       </c>
     </row>
     <row r="20">
@@ -1014,22 +1014,22 @@
         <v>-</v>
       </c>
       <c r="C20">
+        <v>61</v>
+      </c>
+      <c r="D20">
+        <v>-3</v>
+      </c>
+      <c r="E20">
+        <v>-4.6875</v>
+      </c>
+      <c r="F20">
+        <v>62.75</v>
+      </c>
+      <c r="G20">
         <v>64</v>
       </c>
-      <c r="D20">
-        <v>0.75</v>
-      </c>
-      <c r="E20">
-        <v>1.1857707509881423</v>
-      </c>
-      <c r="F20">
-        <v>63</v>
-      </c>
-      <c r="G20">
-        <v>65</v>
-      </c>
       <c r="H20">
-        <v>63</v>
+        <v>60.5</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1038,22 +1038,22 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>14815331</v>
+        <v>20838145</v>
       </c>
       <c r="L20">
-        <v>949666.43975</v>
+        <v>1296498.84575</v>
       </c>
       <c r="M20">
-        <v>274800</v>
+        <v>483300</v>
       </c>
       <c r="N20">
-        <v>64</v>
+        <v>60.75</v>
       </c>
       <c r="O20">
-        <v>64.25</v>
+        <v>61</v>
       </c>
       <c r="P20">
-        <v>258800</v>
+        <v>175200</v>
       </c>
     </row>
     <row r="21">
@@ -1064,22 +1064,22 @@
         <v>-</v>
       </c>
       <c r="C21">
+        <v>72</v>
+      </c>
+      <c r="D21">
+        <v>-0.5</v>
+      </c>
+      <c r="E21">
+        <v>-0.6896551724137931</v>
+      </c>
+      <c r="F21">
         <v>72.5</v>
       </c>
-      <c r="D21">
-        <v>-0.25</v>
-      </c>
-      <c r="E21">
-        <v>-0.3436426116838488</v>
-      </c>
-      <c r="F21">
+      <c r="G21">
         <v>72.75</v>
       </c>
-      <c r="G21">
-        <v>73</v>
-      </c>
       <c r="H21">
-        <v>72.25</v>
+        <v>71.5</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1088,22 +1088,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>1572591</v>
+        <v>3001482</v>
       </c>
       <c r="L21">
-        <v>114134.26675</v>
+        <v>215776.429</v>
       </c>
       <c r="M21">
-        <v>25400</v>
+        <v>136700</v>
       </c>
       <c r="N21">
-        <v>72.5</v>
+        <v>71.75</v>
       </c>
       <c r="O21">
-        <v>72.75</v>
+        <v>72</v>
       </c>
       <c r="P21">
-        <v>154600</v>
+        <v>63900</v>
       </c>
     </row>
     <row r="22">
@@ -1114,46 +1114,46 @@
         <v>-</v>
       </c>
       <c r="C22">
+        <v>67</v>
+      </c>
+      <c r="D22">
+        <v>-0.5</v>
+      </c>
+      <c r="E22">
+        <v>-0.7407407407407407</v>
+      </c>
+      <c r="F22">
         <v>67.5</v>
       </c>
-      <c r="D22">
-        <v>-1</v>
-      </c>
-      <c r="E22">
-        <v>-1.4598540145985401</v>
-      </c>
-      <c r="F22">
-        <v>68.5</v>
-      </c>
       <c r="G22">
-        <v>68.5</v>
+        <v>67.75</v>
       </c>
       <c r="H22">
+        <v>67</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>6480541</v>
+      </c>
+      <c r="L22">
+        <v>435661.81975</v>
+      </c>
+      <c r="M22">
+        <v>103900</v>
+      </c>
+      <c r="N22">
+        <v>67</v>
+      </c>
+      <c r="O22">
         <v>67.25</v>
       </c>
-      <c r="I22">
-        <v>600000</v>
-      </c>
-      <c r="J22">
-        <v>40500</v>
-      </c>
-      <c r="K22">
-        <v>9986259</v>
-      </c>
-      <c r="L22">
-        <v>675593.27775</v>
-      </c>
-      <c r="M22">
-        <v>688400</v>
-      </c>
-      <c r="N22">
-        <v>67.25</v>
-      </c>
-      <c r="O22">
-        <v>67.5</v>
-      </c>
       <c r="P22">
-        <v>110400</v>
+        <v>227700</v>
       </c>
     </row>
     <row r="23">
@@ -1164,22 +1164,22 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="D23">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E23">
-        <v>-1.1494252873563218</v>
+        <v>-0.5813953488372093</v>
       </c>
       <c r="F23">
         <v>17.3</v>
       </c>
       <c r="G23">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="H23">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1188,22 +1188,22 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>37917040</v>
+        <v>48659237</v>
       </c>
       <c r="L23">
-        <v>654660.8281</v>
+        <v>833459.7826</v>
       </c>
       <c r="M23">
-        <v>6309000</v>
+        <v>9581700</v>
       </c>
       <c r="N23">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="O23">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="P23">
-        <v>3186300</v>
+        <v>971100</v>
       </c>
     </row>
     <row r="24">
@@ -1214,46 +1214,46 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>9.9</v>
+        <v>9.75</v>
       </c>
       <c r="D24">
-        <v>0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="E24">
-        <v>0.5076142131979695</v>
+        <v>-1.5151515151515151</v>
       </c>
       <c r="F24">
-        <v>9.9</v>
+        <v>9.85</v>
       </c>
       <c r="G24">
         <v>9.9</v>
       </c>
       <c r="H24">
+        <v>9.75</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>29600861</v>
+      </c>
+      <c r="L24">
+        <v>289544.87305</v>
+      </c>
+      <c r="M24">
+        <v>2546000</v>
+      </c>
+      <c r="N24">
+        <v>9.75</v>
+      </c>
+      <c r="O24">
         <v>9.8</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>17389859</v>
-      </c>
-      <c r="L24">
-        <v>171529.96815</v>
-      </c>
-      <c r="M24">
-        <v>2477700</v>
-      </c>
-      <c r="N24">
-        <v>9.85</v>
-      </c>
-      <c r="O24">
-        <v>9.9</v>
-      </c>
       <c r="P24">
-        <v>4248600</v>
+        <v>303200</v>
       </c>
     </row>
     <row r="25">
@@ -1276,10 +1276,10 @@
         <v>11.8</v>
       </c>
       <c r="G25">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H25">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1288,13 +1288,13 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>8430180</v>
+        <v>2906473</v>
       </c>
       <c r="L25">
-        <v>98138.46029999999</v>
+        <v>34136.7525</v>
       </c>
       <c r="M25">
-        <v>115300</v>
+        <v>877600</v>
       </c>
       <c r="N25">
         <v>11.7</v>
@@ -1303,7 +1303,7 @@
         <v>11.8</v>
       </c>
       <c r="P25">
-        <v>439100</v>
+        <v>334500</v>
       </c>
     </row>
     <row r="26">
@@ -1314,37 +1314,37 @@
         <v>-</v>
       </c>
       <c r="C26">
+        <v>28.25</v>
+      </c>
+      <c r="D26">
+        <v>-0.25</v>
+      </c>
+      <c r="E26">
+        <v>-0.8771929824561403</v>
+      </c>
+      <c r="F26">
         <v>28.5</v>
-      </c>
-      <c r="D26">
-        <v>0.25</v>
-      </c>
-      <c r="E26">
-        <v>0.8849557522123894</v>
-      </c>
-      <c r="F26">
-        <v>28.25</v>
       </c>
       <c r="G26">
         <v>28.5</v>
       </c>
       <c r="H26">
-        <v>28</v>
+        <v>28.25</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>804100</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>22715.825</v>
       </c>
       <c r="K26">
-        <v>5471542</v>
+        <v>2828867</v>
       </c>
       <c r="L26">
-        <v>154774.204</v>
+        <v>79952.18825</v>
       </c>
       <c r="M26">
-        <v>760700</v>
+        <v>1505600</v>
       </c>
       <c r="N26">
         <v>28.25</v>
@@ -1353,7 +1353,7 @@
         <v>28.5</v>
       </c>
       <c r="P26">
-        <v>714100</v>
+        <v>753900</v>
       </c>
     </row>
     <row r="27">
@@ -1364,13 +1364,13 @@
         <v>-</v>
       </c>
       <c r="C27">
-        <v>32.5</v>
+        <v>32.75</v>
       </c>
       <c r="D27">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="E27">
-        <v>-0.7633587786259542</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F27">
         <v>32.75</v>
@@ -1388,13 +1388,13 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>33729036</v>
+        <v>42273305</v>
       </c>
       <c r="L27">
-        <v>1100507.0125</v>
+        <v>1384108.04175</v>
       </c>
       <c r="M27">
-        <v>13937300</v>
+        <v>10710700</v>
       </c>
       <c r="N27">
         <v>32.5</v>
@@ -1403,7 +1403,7 @@
         <v>32.75</v>
       </c>
       <c r="P27">
-        <v>1785800</v>
+        <v>1246100</v>
       </c>
     </row>
     <row r="28">
@@ -1417,34 +1417,34 @@
         <v>165</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>0.6097560975609756</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G28">
-        <v>165.5</v>
+        <v>167.5</v>
       </c>
       <c r="H28">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I28">
-        <v>160000</v>
+        <v>11900</v>
       </c>
       <c r="J28">
-        <v>26240</v>
+        <v>1963.5</v>
       </c>
       <c r="K28">
-        <v>15544249</v>
+        <v>9754541</v>
       </c>
       <c r="L28">
-        <v>2560725.5295</v>
+        <v>1619306.919</v>
       </c>
       <c r="M28">
-        <v>810500</v>
+        <v>918900</v>
       </c>
       <c r="N28">
         <v>164.5</v>
@@ -1453,7 +1453,7 @@
         <v>165</v>
       </c>
       <c r="P28">
-        <v>30300</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="29">
@@ -1476,7 +1476,7 @@
         <v>2.36</v>
       </c>
       <c r="G29">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H29">
         <v>2.34</v>
@@ -1488,22 +1488,22 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>20156462</v>
+        <v>9587384</v>
       </c>
       <c r="L29">
-        <v>47521.32348</v>
+        <v>22535.50924</v>
       </c>
       <c r="M29">
-        <v>521800</v>
+        <v>6964600</v>
       </c>
       <c r="N29">
+        <v>2.34</v>
+      </c>
+      <c r="O29">
         <v>2.36</v>
       </c>
-      <c r="O29">
-        <v>2.38</v>
-      </c>
       <c r="P29">
-        <v>7927400</v>
+        <v>2034200</v>
       </c>
     </row>
     <row r="30">
@@ -1514,23 +1514,23 @@
         <v>-</v>
       </c>
       <c r="C30">
+        <v>42.75</v>
+      </c>
+      <c r="D30">
+        <v>0.25</v>
+      </c>
+      <c r="E30">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="F30">
+        <v>42.75</v>
+      </c>
+      <c r="G30">
+        <v>43</v>
+      </c>
+      <c r="H30">
         <v>42.5</v>
       </c>
-      <c r="D30">
-        <v>-0.25</v>
-      </c>
-      <c r="E30">
-        <v>-0.5847953216374269</v>
-      </c>
-      <c r="F30">
-        <v>42.5</v>
-      </c>
-      <c r="G30">
-        <v>42.75</v>
-      </c>
-      <c r="H30">
-        <v>42.25</v>
-      </c>
       <c r="I30">
         <v>0</v>
       </c>
@@ -1538,13 +1538,13 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>2231778</v>
+        <v>1720777</v>
       </c>
       <c r="L30">
-        <v>94917.6095</v>
+        <v>73573.31375</v>
       </c>
       <c r="M30">
-        <v>242100</v>
+        <v>392400</v>
       </c>
       <c r="N30">
         <v>42.5</v>
@@ -1553,7 +1553,7 @@
         <v>42.75</v>
       </c>
       <c r="P30">
-        <v>159700</v>
+        <v>183000</v>
       </c>
     </row>
     <row r="31">
@@ -1564,13 +1564,13 @@
         <v>-</v>
       </c>
       <c r="C31">
-        <v>55.5</v>
+        <v>55</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="E31">
-        <v>-1.7699115044247788</v>
+        <v>-0.9009009009009009</v>
       </c>
       <c r="F31">
         <v>56</v>
@@ -1579,31 +1579,31 @@
         <v>56.5</v>
       </c>
       <c r="H31">
+        <v>54.75</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>10618744</v>
+      </c>
+      <c r="L31">
+        <v>590772.99275</v>
+      </c>
+      <c r="M31">
+        <v>513300</v>
+      </c>
+      <c r="N31">
         <v>55</v>
       </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>10005330</v>
-      </c>
-      <c r="L31">
-        <v>555531.02575</v>
-      </c>
-      <c r="M31">
-        <v>289500</v>
-      </c>
-      <c r="N31">
+      <c r="O31">
         <v>55.25</v>
       </c>
-      <c r="O31">
-        <v>55.5</v>
-      </c>
       <c r="P31">
-        <v>33800</v>
+        <v>34700</v>
       </c>
     </row>
     <row r="32">
@@ -1617,43 +1617,43 @@
         <v>338</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>0.5952380952380952</v>
+        <v>0</v>
       </c>
       <c r="F32">
+        <v>338</v>
+      </c>
+      <c r="G32">
+        <v>340</v>
+      </c>
+      <c r="H32">
         <v>337</v>
       </c>
-      <c r="G32">
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>2114967</v>
+      </c>
+      <c r="L32">
+        <v>716071.182</v>
+      </c>
+      <c r="M32">
+        <v>34700</v>
+      </c>
+      <c r="N32">
+        <v>338</v>
+      </c>
+      <c r="O32">
         <v>339</v>
       </c>
-      <c r="H32">
-        <v>336</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>2304687</v>
-      </c>
-      <c r="L32">
-        <v>778502.554</v>
-      </c>
-      <c r="M32">
-        <v>487000</v>
-      </c>
-      <c r="N32">
-        <v>337</v>
-      </c>
-      <c r="O32">
-        <v>338</v>
-      </c>
       <c r="P32">
-        <v>211800</v>
+        <v>286100</v>
       </c>
     </row>
     <row r="33">
@@ -1667,20 +1667,20 @@
         <v>24.5</v>
       </c>
       <c r="D33">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>1.2396694214876034</v>
+        <v>0</v>
       </c>
       <c r="F33">
+        <v>24.6</v>
+      </c>
+      <c r="G33">
+        <v>24.8</v>
+      </c>
+      <c r="H33">
         <v>24.4</v>
       </c>
-      <c r="G33">
-        <v>24.7</v>
-      </c>
-      <c r="H33">
-        <v>24.1</v>
-      </c>
       <c r="I33">
         <v>0</v>
       </c>
@@ -1688,13 +1688,13 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>17117094</v>
+        <v>10111603</v>
       </c>
       <c r="L33">
-        <v>418845.7735</v>
+        <v>248609.5797</v>
       </c>
       <c r="M33">
-        <v>443500</v>
+        <v>279800</v>
       </c>
       <c r="N33">
         <v>24.5</v>
@@ -1703,7 +1703,7 @@
         <v>24.6</v>
       </c>
       <c r="P33">
-        <v>289200</v>
+        <v>173100</v>
       </c>
     </row>
     <row r="34">
@@ -1714,46 +1714,46 @@
         <v>-</v>
       </c>
       <c r="C34">
-        <v>43.25</v>
+        <v>42.75</v>
       </c>
       <c r="D34">
-        <v>0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="E34">
-        <v>0.5813953488372093</v>
+        <v>-1.1560693641618498</v>
       </c>
       <c r="F34">
         <v>43</v>
       </c>
       <c r="G34">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="H34">
+        <v>42.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>2498019</v>
+      </c>
+      <c r="L34">
+        <v>106844.8</v>
+      </c>
+      <c r="M34">
+        <v>1337900</v>
+      </c>
+      <c r="N34">
+        <v>42.5</v>
+      </c>
+      <c r="O34">
         <v>42.75</v>
       </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>1622069</v>
-      </c>
-      <c r="L34">
-        <v>69930.36075</v>
-      </c>
-      <c r="M34">
-        <v>325300</v>
-      </c>
-      <c r="N34">
-        <v>43</v>
-      </c>
-      <c r="O34">
-        <v>43.25</v>
-      </c>
       <c r="P34">
-        <v>298900</v>
+        <v>69500</v>
       </c>
     </row>
     <row r="35">
@@ -1764,22 +1764,22 @@
         <v>-</v>
       </c>
       <c r="C35">
+        <v>4.04</v>
+      </c>
+      <c r="D35">
+        <v>-0.02</v>
+      </c>
+      <c r="E35">
+        <v>-0.49261083743842365</v>
+      </c>
+      <c r="F35">
         <v>4.06</v>
       </c>
-      <c r="D35">
-        <v>-0.06</v>
-      </c>
-      <c r="E35">
-        <v>-1.4563106796116505</v>
-      </c>
-      <c r="F35">
+      <c r="G35">
         <v>4.1</v>
       </c>
-      <c r="G35">
-        <v>4.12</v>
-      </c>
       <c r="H35">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1788,22 +1788,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>18301546</v>
+        <v>35674628</v>
       </c>
       <c r="L35">
-        <v>74524.31034</v>
+        <v>144373.1414</v>
       </c>
       <c r="M35">
-        <v>2654200</v>
+        <v>1820600</v>
       </c>
       <c r="N35">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="O35">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="P35">
-        <v>499100</v>
+        <v>118300</v>
       </c>
     </row>
     <row r="36">
@@ -1817,13 +1817,13 @@
         <v>102.5</v>
       </c>
       <c r="D36">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>-0.4854368932038835</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>103</v>
+        <v>102.5</v>
       </c>
       <c r="G36">
         <v>103</v>
@@ -1838,13 +1838,13 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>3757061</v>
+        <v>3130384</v>
       </c>
       <c r="L36">
-        <v>385313.0485</v>
+        <v>320852.1005</v>
       </c>
       <c r="M36">
-        <v>312300</v>
+        <v>38100</v>
       </c>
       <c r="N36">
         <v>102.5</v>
@@ -1853,7 +1853,7 @@
         <v>103</v>
       </c>
       <c r="P36">
-        <v>1323400</v>
+        <v>1244600</v>
       </c>
     </row>
     <row r="37">
@@ -1864,22 +1864,22 @@
         <v>-</v>
       </c>
       <c r="C37">
+        <v>1.41</v>
+      </c>
+      <c r="D37">
+        <v>-0.01</v>
+      </c>
+      <c r="E37">
+        <v>-0.704225352112676</v>
+      </c>
+      <c r="F37">
         <v>1.42</v>
       </c>
-      <c r="D37">
-        <v>-0.03</v>
-      </c>
-      <c r="E37">
-        <v>-2.0689655172413794</v>
-      </c>
-      <c r="F37">
-        <v>1.44</v>
-      </c>
       <c r="G37">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="H37">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>194236716</v>
+        <v>176495947</v>
       </c>
       <c r="L37">
-        <v>276844.8389</v>
+        <v>248569.87536</v>
       </c>
       <c r="M37">
-        <v>17077300</v>
+        <v>32377900</v>
       </c>
       <c r="N37">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P37">
-        <v>21403900</v>
+        <v>27769300</v>
       </c>
     </row>
     <row r="38">
@@ -1914,19 +1914,19 @@
         <v>-</v>
       </c>
       <c r="C38">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>-0.6172839506172839</v>
       </c>
       <c r="F38">
         <v>16.3</v>
       </c>
       <c r="G38">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="H38">
         <v>16.1</v>
@@ -1938,22 +1938,22 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>16289493</v>
+        <v>11030952</v>
       </c>
       <c r="L38">
-        <v>264277.7181</v>
+        <v>177788.1126</v>
       </c>
       <c r="M38">
-        <v>1328900</v>
+        <v>3467300</v>
       </c>
       <c r="N38">
+        <v>16.1</v>
+      </c>
+      <c r="O38">
         <v>16.2</v>
       </c>
-      <c r="O38">
-        <v>16.3</v>
-      </c>
       <c r="P38">
-        <v>1582700</v>
+        <v>1787400</v>
       </c>
     </row>
     <row r="39">
@@ -1967,10 +1967,10 @@
         <v>3.9</v>
       </c>
       <c r="D39">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>-0.5102040816326531</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>3.92</v>
@@ -1988,22 +1988,22 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>73616885</v>
+        <v>69634122</v>
       </c>
       <c r="L39">
-        <v>286207.30916</v>
+        <v>271734.08660000004</v>
       </c>
       <c r="M39">
-        <v>6303600</v>
+        <v>46300</v>
       </c>
       <c r="N39">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="O39">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="P39">
-        <v>1586700</v>
+        <v>7688900</v>
       </c>
     </row>
   </sheetData>
